--- a/docs/simmevator-parts-cost.xlsx
+++ b/docs/simmevator-parts-cost.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -741,12 +741,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Mini360 3.3V Buck Converter (5 pcs)</t>
+          <t>MP1584EN 5V Buck Converter (5 pcs)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0BVFYXPQ8</t>
+          <t>https://www.amazon.com/dp/B0B779ZYN1</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -770,7 +770,7 @@
         <v/>
       </c>
       <c r="J8" s="6" t="n">
-        <v>8.69</v>
+        <v>8.99</v>
       </c>
       <c r="K8" s="6">
         <f>I8*J8</f>
@@ -945,46 +945,88 @@
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="K14" s="8">
-        <f>SUM(K4:K12)</f>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Command Poster Strips (64 strips)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/dp/B0751VFF2X</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H13" s="3">
+        <f>E13+F13+G13</f>
+        <v/>
+      </c>
+      <c r="I13" s="3">
+        <f>ROUNDUP(H13/D13,0)</f>
+        <v/>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="K13" s="6">
+        <f>I13*J13</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>Sales Tax Rate (Boston, MA)</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="n">
-        <v>0.0625</v>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="K15" s="8">
+        <f>SUM(K4:K13)</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="I16" s="7" t="inlineStr">
         <is>
+          <t>Sales Tax Rate (Boston, MA)</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>0.0625</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="I17" s="7" t="inlineStr">
+        <is>
           <t>Sales Tax</t>
         </is>
       </c>
-      <c r="K16" s="8">
-        <f>ROUND(K14*K15,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="I17" s="10" t="inlineStr">
+      <c r="K17" s="8">
+        <f>ROUND(K15*K16,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="K17" s="11">
-        <f>K14+K16</f>
+      <c r="K18" s="11">
+        <f>K15+K17</f>
         <v/>
       </c>
     </row>
@@ -993,7 +1035,7 @@
     <mergeCell ref="I16:J16"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I18:J18"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
@@ -1005,6 +1047,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
